--- a/入职、日报周报/2026-Q2-绩效-物流服务交付事业部-数字货运事业部-前端部-王新骏.xlsx
+++ b/入职、日报周报/2026-Q2-绩效-物流服务交付事业部-数字货运事业部-前端部-王新骏.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26860" windowHeight="15580" activeTab="1"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="研发岗" sheetId="14" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <t>季度绩效评价表</t>
   </si>
   <si>
-    <t xml:space="preserve">姓名： xxxx          岗位：   高级前端开发                  部门：         物流服务交付事业部-数字货运事业部-前端部                             </t>
+    <t xml:space="preserve">姓名： 王新骏          岗位：   高级前端开发                  部门：    物流服务交付事业群/业务平台事业部/前端部/结算前端组                       </t>
   </si>
   <si>
     <t>评价维度</t>
@@ -75,7 +75,7 @@
 签字日期：</t>
   </si>
   <si>
-    <t xml:space="preserve">              姓名：  xxx                                                        岗位：     前端                                                          部门：物流服务交付事业部-数字货运事业部-前端部</t>
+    <t xml:space="preserve">              姓名：  王新骏                                                        岗位： 高级前端开发                                                          部门：物流服务交付事业群/业务平台事业部/前端部/结算前端组</t>
   </si>
   <si>
     <t>绩效指标</t>
@@ -116,9 +116,8 @@
     <t>工作任务按计划、交付标准完成率</t>
   </si>
   <si>
-    <t>任务完成率：承接需求迭代、问题修复等任务共 40 余项，覆盖 3PL、货主端 APP、易达宝撮合平台等业务线，整体任务按计划完成率达95%，个别项因需求变更调整后仍按期交付。
-交付质量：所有上线需求均通过测试验证，未出现线上重大缺陷及用户体验问题，项目整体交付达成率100%，保障系统稳定运行
-项目整体交付达成率100%。 参与的项目均按时上线，上线后运行稳定，客户反馈良好。</t>
+    <t>任务完成率：本季度个人主导并高质量完成网货成本优化（C85.8）、企业树组件开发（CHJY-19979）、网货钱包排版优化（C103.3）、运单结算风控逻辑优化（C84.8）及货主端快速交付系列（C96.6/C105.5/C108.8）等核心需求迭代，覆盖3PL结算平台、4PL管理后台、货主端APP等多业务线，整体任务按计划完成率达95%以上，交付达成率100%，所有需求均按期上线。
+交付质量：重点保障C85.8成本差价率模块、企业树组件跨3PL/4PL两端开发及货主端快速交付系列（C96.6/C105.5/C108.8）等复杂业务的平稳落地，上线后运行稳定，无重大生产事故；针对线上问题实现快速响应与修复，客户反馈良好，有力支撑了结算对账能力建设与货主端体验优化目标的达成。</t>
   </si>
   <si>
     <t>满分100：包含以下二项内容：
@@ -145,7 +144,8 @@
     <t>用户体验、生产问题</t>
   </si>
   <si>
-    <t>本季度交付质量稳定，无生产事故及核心用户体验问题；提测后无重大 Bug，代码质量较高，技术文档完整准确；严格遵循产研规范执行全流程，流程合规度 100%，各项指标均达标。</t>
+    <t>交付质量：本季度代码交付质量稳定，提测前均进行自测，提测后无重大Bug；C85.8成本差价率模块（统一组件逻辑与UI分离、原一二级拆分为独立组件）与企业树组件跨端开发（CHJY-19979）两项核心模块开发投入周期长、架构复杂度高，交付后运行稳定，无核心用户体验投诉。
+专业技术与规范：严格遵循开发规范执行全流程，需求改动同步维护改动清单与接口说明文档，技术文档完整准确且及时更新；主动与后端沟通对接，确保技术实现与业务目标高度对齐，流程合规度100%。</t>
   </si>
   <si>
     <t>交付质量，满分100
@@ -188,18 +188,10 @@
     <t>工作职责与分工、高效协作、执行力、主动性</t>
   </si>
   <si>
-    <t>1. 责任心与协作
-积极主动承接各项工作任务，高效配合团队分工，与产品、测试、后端同事紧密协作推进需求落地，主动同步进度、对齐风险，保障跨端联调与上线流程顺畅，执行效果稳定超出预期。
-2. 主动思考与沟通
-独立思考需求实现方案与用户体验优化点，主动与业务方、技术伙伴沟通，沟通逻辑清晰、重点突出，能快速对齐认知并推动问题解决，保障开发效率与交付质量。
-3. 团队配合与经验分享
-主动配合团队安排，高频分享前端开发规范、接口文档梳理等经验，同事求助时及时提供协助，参与团队知识沉淀，无协作推诿情况，助力团队整体效率提升。
-4. 面对问题的态度
-主动承担问题责任，积极推动线上问题、需求偏差的定位与解决，不回避挑战，关键任务安排后主动承接，以务实态度保障项目进度与系统稳定。
-5. 关注业务与用户需求
-按要求对接业务方获取反馈，响应需求优化建议，针对用户体验问题快速调整实现，保障客户无负面评价，贴合业务场景完善功能细节。
-6.学习提升与知识传承
-保持基础学习行为，配合输出接口文档、开发总结等知识内容，带教新人时耐心解答疑问，助力新人快速融入团队，基本达成团队学习与传承要求。</t>
+    <t>1. 责任心与协作：积极主动承接网货成本优化（C85.8）、企业树组件开发（CHJY-19979）等高优先级且开发周期较长的核心任务，高效配合产品、测试及后端同事，在跨3PL/4PL两端联调中主动同步进度、对齐风险，保障联调顺畅。
+2. 主动思考与沟通：针对C85.8成本差价率模块的组件化拆分，独立设计逻辑与UI分离方案、将原一二级拆分为独立组件，提升模块可维护性与复用性；针对企业树组件跨端历史缓存问题，主动调研新版接口开发方案；主动探索并沉淀AI辅助开发相关实践，提升开发效率。
+3. 扛责担当与客户导向：CHJY-17879体验升级专项中主动承接历史遗留问题，不回避挑战；密切关注业务方反馈，QLMR-25352运单付款对账状态筛选、C84.8风控逻辑优化等需求中按业务方诉求快速响应并交付。
+4. 人才发展与知识传承：保持高频学习，主动梳理企业树组件开发、DCS接口适配等技术难点并形成改动清单与接口文档；沉淀AI辅助开发实践，持续提升开发效率与技术储备。</t>
   </si>
   <si>
     <t>1、积极主动执行工作任务并主动做好团队成员间的协同分工，工作执行效果经常超出上级预期（90-100分）
@@ -293,9 +285,9 @@
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="177" formatCode="0.0_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -338,6 +330,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
@@ -345,13 +338,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -722,6 +714,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -813,15 +814,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1102,232 +1094,232 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyProtection="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1335,37 +1327,37 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1741,86 +1733,78 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="68.25" customHeight="1" spans="2:7">
+    <row r="4" customFormat="1" ht="177" spans="2:7">
       <c r="B4" s="71" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="72">
         <v>0.3</v>
       </c>
-      <c r="D4" s="68" t="str">
+      <c r="D4" s="73" t="str">
         <f>研发岗明细!H4</f>
-        <v>任务完成率：承接需求迭代、问题修复等任务共 40 余项，覆盖 3PL、货主端 APP、易达宝撮合平台等业务线，整体任务按计划完成率达95%，个别项因需求变更调整后仍按期交付。
-交付质量：所有上线需求均通过测试验证，未出现线上重大缺陷及用户体验问题，项目整体交付达成率100%，保障系统稳定运行
-项目整体交付达成率100%。 参与的项目均按时上线，上线后运行稳定，客户反馈良好。</v>
+        <v>任务完成率：本季度个人主导并高质量完成网货成本优化（C85.8）、企业树组件开发（CHJY-19979）、网货钱包排版优化（C103.3）、运单结算风控逻辑优化（C84.8）及货主端快速交付系列（C96.6/C105.5/C108.8）等核心需求迭代，覆盖3PL结算平台、4PL管理后台、货主端APP等多业务线，整体任务按计划完成率达95%以上，交付达成率100%，所有需求均按期上线。
+交付质量：重点保障C85.8成本差价率模块、企业树组件跨3PL/4PL两端开发及货主端快速交付系列（C96.6/C105.5/C108.8）等复杂业务的平稳落地，上线后运行稳定，无重大生产事故；针对线上问题实现快速响应与修复，客户反馈良好，有力支撑了结算对账能力建设与货主端体验优化目标的达成。</v>
       </c>
       <c r="E4" s="69">
         <v>96</v>
       </c>
       <c r="F4" s="69">
         <f>研发岗明细!N4</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="G4" s="69">
         <f t="shared" ref="G4:G6" si="0">F4*C4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" customFormat="1" ht="61.25" customHeight="1" spans="2:7">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="123" spans="2:7">
       <c r="B5" s="71" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="72">
         <v>0.4</v>
       </c>
-      <c r="D5" s="68" t="str">
+      <c r="D5" s="73" t="str">
         <f>研发岗明细!H7</f>
-        <v>本季度交付质量稳定，无生产事故及核心用户体验问题；提测后无重大 Bug，代码质量较高，技术文档完整准确；严格遵循产研规范执行全流程，流程合规度 100%，各项指标均达标。</v>
+        <v>交付质量：本季度代码交付质量稳定，提测前均进行自测，提测后无重大Bug；C85.8成本差价率模块（统一组件逻辑与UI分离、原一二级拆分为独立组件）与企业树组件跨端开发（CHJY-19979）两项核心模块开发投入周期长、架构复杂度高，交付后运行稳定，无核心用户体验投诉。
+专业技术与规范：严格遵循开发规范执行全流程，需求改动同步维护改动清单与接口说明文档，技术文档完整准确且及时更新；主动与后端沟通对接，确保技术实现与业务目标高度对齐，流程合规度100%。</v>
       </c>
       <c r="E5" s="69">
         <v>96</v>
       </c>
       <c r="F5" s="69">
         <f>研发岗明细!N7</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="G5" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="54.8" customHeight="1" spans="2:7">
-      <c r="B6" s="73" t="s">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="218" spans="2:7">
+      <c r="B6" s="74" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="72">
         <v>0.3</v>
       </c>
-      <c r="D6" s="74" t="str">
+      <c r="D6" s="73" t="str">
         <f>研发岗明细!H12</f>
-        <v>1. 责任心与协作
-积极主动承接各项工作任务，高效配合团队分工，与产品、测试、后端同事紧密协作推进需求落地，主动同步进度、对齐风险，保障跨端联调与上线流程顺畅，执行效果稳定超出预期。
-2. 主动思考与沟通
-独立思考需求实现方案与用户体验优化点，主动与业务方、技术伙伴沟通，沟通逻辑清晰、重点突出，能快速对齐认知并推动问题解决，保障开发效率与交付质量。
-3. 团队配合与经验分享
-主动配合团队安排，高频分享前端开发规范、接口文档梳理等经验，同事求助时及时提供协助，参与团队知识沉淀，无协作推诿情况，助力团队整体效率提升。
-4. 面对问题的态度
-主动承担问题责任，积极推动线上问题、需求偏差的定位与解决，不回避挑战，关键任务安排后主动承接，以务实态度保障项目进度与系统稳定。
-5. 关注业务与用户需求
-按要求对接业务方获取反馈，响应需求优化建议，针对用户体验问题快速调整实现，保障客户无负面评价，贴合业务场景完善功能细节。
-6.学习提升与知识传承
-保持基础学习行为，配合输出接口文档、开发总结等知识内容，带教新人时耐心解答疑问，助力新人快速融入团队，基本达成团队学习与传承要求。</v>
+        <v>1. 责任心与协作：积极主动承接网货成本优化（C85.8）、企业树组件开发（CHJY-19979）等高优先级且开发周期较长的核心任务，高效配合产品、测试及后端同事，在跨3PL/4PL两端联调中主动同步进度、对齐风险，保障联调顺畅。
+2. 主动思考与沟通：针对C85.8成本差价率模块的组件化拆分，独立设计逻辑与UI分离方案、将原一二级拆分为独立组件，提升模块可维护性与复用性；针对企业树组件跨端历史缓存问题，主动调研新版接口开发方案；主动探索并沉淀AI辅助开发相关实践，提升开发效率。
+3. 扛责担当与客户导向：CHJY-17879体验升级专项中主动承接历史遗留问题，不回避挑战；密切关注业务方反馈，QLMR-25352运单付款对账状态筛选、C84.8风控逻辑优化等需求中按业务方诉求快速响应并交付。
+4. 人才发展与知识传承：保持高频学习，主动梳理企业树组件开发、DCS接口适配等技术难点并形成改动清单与接口文档；沉淀AI辅助开发实践，持续提升开发效率与技术储备。</v>
       </c>
       <c r="E6" s="70">
         <v>95</v>
       </c>
       <c r="F6" s="69">
         <f>研发岗明细!N12</f>
-        <v>0</v>
+        <v>7.12</v>
       </c>
       <c r="G6" s="69">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.136</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="22.05" customHeight="1" spans="2:7">
@@ -1833,7 +1817,7 @@
       <c r="F7" s="69"/>
       <c r="G7" s="69">
         <f>SUM(G4:G6)</f>
-        <v>0</v>
+        <v>7.176</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="42.45" customHeight="1" spans="2:7">
@@ -1894,499 +1878,523 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="57"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="8"/>
       <c r="N1" s="5"/>
     </row>
     <row r="2" s="1" customFormat="1" ht="21" customHeight="1" spans="2:14">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="58"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="12"/>
       <c r="N2" s="5"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="45.4" customHeight="1" spans="2:14">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="44" t="s">
+      <c r="J3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="45" t="s">
+      <c r="K3" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="45" t="s">
+      <c r="L3" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="59" t="s">
+      <c r="M3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="N3" s="59" t="s">
+      <c r="N3" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" ht="133.15" customHeight="1" spans="2:14">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="21">
         <v>1</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="22">
         <v>0.6</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="23">
         <v>100</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="46" t="s">
+      <c r="I4" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="60">
+      <c r="J4" s="26">
+        <v>90</v>
+      </c>
+      <c r="K4" s="26"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="28">
         <f>J4*0.1+K4*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="61">
+        <v>9</v>
+      </c>
+      <c r="N4" s="29">
         <f>(M4*F4+M5*F5)*0.8+L4*0.2</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" ht="68" spans="2:14">
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="30" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="33">
         <v>0.4</v>
       </c>
-      <c r="G5" s="32">
+      <c r="G5" s="34">
         <v>100</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="49" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="60">
+      <c r="J5" s="27">
+        <v>90</v>
+      </c>
+      <c r="K5" s="27"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="28">
         <f t="shared" ref="M4:M10" si="0">J5*0.1+K5*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="29"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="6" customHeight="1" spans="2:14">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="62"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="38"/>
       <c r="N6" s="5"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="84" spans="2:14">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="41">
         <v>1</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="42">
         <v>0.3</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="43">
         <v>100</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="52"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="60">
+      <c r="J7" s="46">
+        <v>90</v>
+      </c>
+      <c r="K7" s="43"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N7" s="61">
+        <v>9</v>
+      </c>
+      <c r="N7" s="29">
         <f>(M7*F7+M8*F8+M9*F9+M10*F10)*0.8+L7*0.2</f>
-        <v>0</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" ht="40.9" customHeight="1" spans="2:14">
-      <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="19"/>
+      <c r="C8" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="36" t="s">
+      <c r="D8" s="31"/>
+      <c r="E8" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="22">
         <v>0.3</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="23">
         <v>100</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="46" t="s">
+      <c r="H8" s="44"/>
+      <c r="I8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="47"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="60">
+      <c r="J8" s="26">
+        <v>90</v>
+      </c>
+      <c r="K8" s="23"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N8" s="29"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="48" customHeight="1" spans="2:14">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="36" t="s">
+      <c r="B9" s="19"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="22">
         <v>0.3</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="23">
         <v>100</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="46" t="s">
+      <c r="H9" s="44"/>
+      <c r="I9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="47"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="33"/>
-      <c r="M9" s="60">
+      <c r="J9" s="26">
+        <v>90</v>
+      </c>
+      <c r="K9" s="23"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N9" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N9" s="29"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="51.6" customHeight="1" spans="2:14">
-      <c r="B10" s="13"/>
-      <c r="C10" s="14" t="s">
+      <c r="B10" s="30"/>
+      <c r="C10" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="31"/>
+      <c r="E10" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="48">
         <v>0.1</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="49">
         <v>100</v>
       </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="53" t="s">
+      <c r="H10" s="44"/>
+      <c r="I10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="33"/>
-      <c r="M10" s="60">
+      <c r="J10" s="27">
+        <v>90</v>
+      </c>
+      <c r="K10" s="49"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N10" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N10" s="29"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="6" customHeight="1" spans="2:14">
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="62"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="38"/>
       <c r="N11" s="5"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="168.6" customHeight="1" spans="2:14">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="41">
         <v>1</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="E12" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="42">
         <v>0.3</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="52">
         <v>100</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="51" t="s">
+      <c r="I12" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="J12" s="52"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="60">
+      <c r="J12" s="46">
+        <v>90</v>
+      </c>
+      <c r="K12" s="40"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="28">
         <f t="shared" ref="M12:M17" si="1">J12*0.1+K12*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="61">
+        <v>9</v>
+      </c>
+      <c r="N12" s="29">
         <f>(M12*F12+M13*F13+M14*F14+M15*F15+M16*F16+M17*F17)*0.8+L12*0.2</f>
-        <v>0</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="192.6" customHeight="1" spans="2:14">
-      <c r="B13" s="10"/>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="19"/>
+      <c r="C13" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="11" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="22">
         <v>0.2</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="54">
         <v>100</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="54" t="s">
+      <c r="H13" s="53"/>
+      <c r="I13" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="J13" s="47"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="60">
+      <c r="J13" s="26">
+        <v>90</v>
+      </c>
+      <c r="K13" s="20"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N13" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N13" s="29"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="178" customHeight="1" spans="2:14">
-      <c r="B14" s="10"/>
-      <c r="C14" s="11" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="11" t="s">
+      <c r="D14" s="31"/>
+      <c r="E14" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="56">
         <v>0.2</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="23">
         <v>100</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="36" t="s">
+      <c r="H14" s="53"/>
+      <c r="I14" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="60">
+      <c r="J14" s="57">
+        <v>90</v>
+      </c>
+      <c r="K14" s="57"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N14" s="29"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="173" customHeight="1" spans="2:14">
-      <c r="B15" s="10"/>
-      <c r="C15" s="11" t="s">
+      <c r="B15" s="19"/>
+      <c r="C15" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="11" t="s">
+      <c r="D15" s="31"/>
+      <c r="E15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="42">
+      <c r="F15" s="56">
         <v>0.1</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="23">
         <v>100</v>
       </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="36" t="s">
+      <c r="H15" s="53"/>
+      <c r="I15" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="60">
+      <c r="J15" s="57">
+        <v>90</v>
+      </c>
+      <c r="K15" s="57"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="61"/>
+        <v>9</v>
+      </c>
+      <c r="N15" s="29"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="171" customHeight="1" spans="2:14">
-      <c r="B16" s="10"/>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="19"/>
+      <c r="C16" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="11" t="s">
+      <c r="D16" s="31"/>
+      <c r="E16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="56">
         <v>0.1</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="23">
         <v>100</v>
       </c>
-      <c r="H16" s="40"/>
-      <c r="I16" s="36" t="s">
+      <c r="H16" s="53"/>
+      <c r="I16" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="60">
+      <c r="J16" s="57">
+        <v>85</v>
+      </c>
+      <c r="K16" s="57"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="61"/>
+        <v>8.5</v>
+      </c>
+      <c r="N16" s="29"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="175" customHeight="1" spans="2:14">
-      <c r="B17" s="10"/>
-      <c r="C17" s="11" t="s">
+      <c r="B17" s="19"/>
+      <c r="C17" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="11" t="s">
+      <c r="D17" s="40"/>
+      <c r="E17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="42">
+      <c r="F17" s="56">
         <v>0.1</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="23">
         <v>100</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="36" t="s">
+      <c r="H17" s="52"/>
+      <c r="I17" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="60">
+      <c r="J17" s="57">
+        <v>85</v>
+      </c>
+      <c r="K17" s="57"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="28">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="61"/>
+        <v>8.5</v>
+      </c>
+      <c r="N17" s="29"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="41.45" customHeight="1" spans="2:14">
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="63">
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+      <c r="J18" s="59"/>
+      <c r="K18" s="59"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="61">
         <f>N4*0.3+N7*0.4+N12*0.3</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="64"/>
+        <v>7.176</v>
+      </c>
+      <c r="N18" s="62"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="49" customHeight="1" spans="2:14">
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="22" t="s">
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="64"/>
+      <c r="I19" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="23"/>
-      <c r="K19" s="23"/>
-      <c r="L19" s="23"/>
+      <c r="J19" s="64"/>
+      <c r="K19" s="64"/>
+      <c r="L19" s="64"/>
       <c r="M19" s="65"/>
       <c r="N19" s="5"/>
     </row>
@@ -2421,4 +2429,20 @@
   <pageSetup paperSize="9" scale="48" fitToWidth="0" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
+  <rangeList sheetStid="14" master="" otherUserPermission="visible"/>
+  <rangeList sheetStid="5" master="" otherUserPermission="visible"/>
+</allowEditUser>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>